--- a/docs/Product Milestones.xlsx
+++ b/docs/Product Milestones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxbi\Sella\verify-prototype\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F994C414-21CB-4BDB-93D8-FABA45A58EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558D87D2-A79A-4B1C-ADE2-54B08723817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{962ED2F9-E290-4F1F-9721-0DA74243B431}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
   <si>
     <t>Milestone</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Aim for end of this weekend</t>
+  </si>
+  <si>
+    <t>MBI Lookup Capability</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D324CA6-C65D-4AA8-8F63-301F40013297}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -552,6 +555,9 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
@@ -566,6 +572,9 @@
       <c r="B3" t="s">
         <v>12</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
@@ -578,13 +587,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -592,13 +601,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -606,24 +618,30 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -631,10 +649,16 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -642,7 +666,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -653,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -664,7 +691,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
@@ -672,13 +699,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -686,13 +713,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -700,13 +724,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -714,12 +741,32 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
       </c>
       <c r="E15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
         <v>32</v>
       </c>
     </row>

--- a/docs/Product Milestones.xlsx
+++ b/docs/Product Milestones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxbi\Sella\verify-prototype\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sellahealthmobileapp\verify-prototype\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558D87D2-A79A-4B1C-ADE2-54B08723817B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936C959-00F9-45E4-834C-B545031DB69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{962ED2F9-E290-4F1F-9721-0DA74243B431}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{962ED2F9-E290-4F1F-9721-0DA74243B431}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,13 +134,26 @@
     <t>Allows for resource flexibility per client size</t>
   </si>
   <si>
-    <t>Microsoft Entra ID - add passkey</t>
-  </si>
-  <si>
     <t>Aim for end of this weekend</t>
   </si>
   <si>
     <t>MBI Lookup Capability</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Microsoft Entra ID - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add passkey</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -522,16 +535,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D324CA6-C65D-4AA8-8F63-301F40013297}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -548,7 +561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -565,7 +578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -582,12 +595,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -596,7 +609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -613,7 +626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -630,7 +643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -644,7 +657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -661,7 +674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -675,7 +688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -686,7 +699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -697,7 +710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -708,7 +721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -719,7 +732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -736,7 +749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -750,10 +763,10 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -767,7 +780,7 @@
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
